--- a/jentech/dist/20261025_健策模型_v0.1.1.xlsx
+++ b/jentech/dist/20261025_健策模型_v0.1.1.xlsx
@@ -7390,7 +7390,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7589,7 +7589,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7710,7 +7710,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7831,7 +7831,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7952,7 +7952,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8073,7 +8073,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/jentech/dist/20261025_健策模型_v0.1.1.xlsx
+++ b/jentech/dist/20261025_健策模型_v0.1.1.xlsx
@@ -5036,7 +5036,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5055,7 +5055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5443,7 +5443,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5462,7 +5462,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5665,7 +5665,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5684,7 +5684,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5906,7 +5906,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5925,7 +5925,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6185,7 +6185,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6204,7 +6204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6407,7 +6407,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6426,7 +6426,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6629,7 +6629,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6648,7 +6648,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6917,7 +6917,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6936,7 +6936,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/jentech/dist/20261025_健策模型_v0.1.1.xlsx
+++ b/jentech/dist/20261025_健策模型_v0.1.1.xlsx
@@ -7371,26 +7371,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7570,26 +7570,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7691,26 +7691,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7812,26 +7812,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7933,26 +7933,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8054,26 +8054,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -43566,7 +43566,7 @@
         <v>205</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="G68" s="8" t="s">
         <v>34</v>
@@ -43658,7 +43658,7 @@
         <v>205</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>34</v>
@@ -43750,7 +43750,7 @@
         <v>205</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>34</v>
@@ -43842,7 +43842,7 @@
         <v>196</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>34</v>
@@ -43911,7 +43911,7 @@
         <v>196</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G83" s="8" t="s">
         <v>34</v>
@@ -43934,7 +43934,7 @@
         <v>196</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>34</v>
@@ -44003,7 +44003,7 @@
         <v>196</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>34</v>
@@ -44026,7 +44026,7 @@
         <v>196</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>34</v>
@@ -44095,7 +44095,7 @@
         <v>196</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>34</v>
@@ -46617,7 +46617,7 @@
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">PL!D128</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="D15" s="21" t="n">
         <f aca="false">PL!E128</f>
@@ -46671,7 +46671,7 @@
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">avshB_26</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">avshB_27</f>
@@ -46683,7 +46683,7 @@
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">avshB_29</f>
-        <v>0.424088494949175</v>
+        <v>0.424088494949176</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>545</v>
@@ -46698,7 +46698,7 @@
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">C17+C16</f>
-        <v>0.498927641116676</v>
+        <v>0.498927641116677</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">D17+D16</f>
@@ -46710,7 +46710,7 @@
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">F17+F16</f>
-        <v>0.449088494949175</v>
+        <v>0.449088494949176</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>547</v>
@@ -48527,7 +48527,7 @@
       </c>
       <c r="D81" s="24" t="n">
         <f aca="false">lmkA_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E81" s="24" t="n">
         <f aca="false">lmkA_27*1</f>
@@ -49666,7 +49666,7 @@
       </c>
       <c r="D128" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E128" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -50805,7 +50805,7 @@
       </c>
       <c r="D175" s="24" t="n">
         <f aca="false">lmkC_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E175" s="24" t="n">
         <f aca="false">lmkC_27*1</f>
@@ -53641,15 +53641,15 @@
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">avshA_29+PL!G82</f>
-        <v>0.469088494949175</v>
+        <v>0.469088494949176</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">avshB_29+PL!G129</f>
-        <v>0.449088494949175</v>
+        <v>0.449088494949176</v>
       </c>
       <c r="G23" s="18" t="n">
         <f aca="false">avshC_29+PL!G176</f>
-        <v>0.434088494949175</v>
+        <v>0.434088494949176</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>802</v>
@@ -55719,7 +55719,7 @@
       </c>
       <c r="D71" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E71" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -56858,7 +56858,7 @@
       </c>
       <c r="D118" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E118" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -57997,7 +57997,7 @@
       </c>
       <c r="D165" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E165" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -59136,7 +59136,7 @@
       </c>
       <c r="D212" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E212" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -60275,7 +60275,7 @@
       </c>
       <c r="D259" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E259" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -61414,7 +61414,7 @@
       </c>
       <c r="D306" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E306" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -62553,7 +62553,7 @@
       </c>
       <c r="D353" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E353" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -63692,7 +63692,7 @@
       </c>
       <c r="D400" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E400" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -64831,7 +64831,7 @@
       </c>
       <c r="D447" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E447" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -65970,7 +65970,7 @@
       </c>
       <c r="D494" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E494" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -67109,7 +67109,7 @@
       </c>
       <c r="D541" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E541" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -68248,7 +68248,7 @@
       </c>
       <c r="D588" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E588" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -69387,7 +69387,7 @@
       </c>
       <c r="D635" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E635" s="24" t="n">
         <f aca="false">lmkB_27*mf_lo</f>
@@ -70526,7 +70526,7 @@
       </c>
       <c r="D682" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E682" s="24" t="n">
         <f aca="false">lmkB_27*mf_hi</f>
@@ -71665,7 +71665,7 @@
       </c>
       <c r="D729" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E729" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -72804,7 +72804,7 @@
       </c>
       <c r="D776" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E776" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -73943,7 +73943,7 @@
       </c>
       <c r="D823" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E823" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -75082,7 +75082,7 @@
       </c>
       <c r="D870" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E870" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -76221,7 +76221,7 @@
       </c>
       <c r="D917" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E917" s="24" t="n">
         <f aca="false">lmkB_27*1</f>
@@ -77360,7 +77360,7 @@
       </c>
       <c r="D964" s="24" t="n">
         <f aca="false">lmkB_26</f>
-        <v>4.5136875859587</v>
+        <v>4.51368758595869</v>
       </c>
       <c r="E964" s="24" t="n">
         <f aca="false">lmkB_27*1</f>

--- a/jentech/dist/20261025_健策模型_v0.1.1.xlsx
+++ b/jentech/dist/20261025_健策模型_v0.1.1.xlsx
@@ -11493,26 +11493,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -11914,26 +11914,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -11952,7 +11952,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PL!D109:G109</t>
+      <t xml:space="preserve">PL!D111:G111</t>
     </r>
   </si>
   <si>
@@ -12248,26 +12248,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12286,7 +12286,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PL!D150:G150</t>
+      <t xml:space="preserve">PL!D154:G154</t>
     </r>
   </si>
   <si>
@@ -12563,26 +12563,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12851,26 +12851,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12889,7 +12889,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PL!D113:G113</t>
+      <t xml:space="preserve">PL!D115:G115</t>
     </r>
   </si>
   <si>
@@ -13109,26 +13109,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">avc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">奇鋐模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">avc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">奇鋐個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13147,7 +13147,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PL!D154:G154</t>
+      <t xml:space="preserve">PL!D158:G158</t>
     </r>
   </si>
   <si>
